--- a/рекомендации/Рекомендации_по_округам.xlsx
+++ b/рекомендации/Рекомендации_по_округам.xlsx
@@ -504,17 +504,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (122), ТС#3 (7) и ТС#4 (1). Минерализация во всех пробах в пределах 1000 мг/л. Повышенная мутность (&gt;5 NTU): ТС#2. Распределение: ограниченно пригодная — 1, высокий риск — 2, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (122), ТС#3 (7) и ТС#4 (1). Минерализация во всех пробах в пределах 1000 мг/л. Повышенная мутность (&gt;5 NTU): ТС#2. Распределение: ограниченно пригодная – 1, высокий риск – 2, критическая – 1.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>• Требуются восстановительные мероприятия: ограничение выпаса на участках ТС#1, ТС#2, ТС#3 и ТС#4, поверхностное улучшение с подсевом житняка, пырея или костреца.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • Уплотнение на ТС#3 и ТС#4: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Источники с E. coli (ТС#1, ТС#3, ТС#4) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
-• Как основной источник поения в округе предпочтительна ТС#2 (ограниченно пригодная, E. coli 0, TDS 136 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#2 (ограниченно пригодная, E. coli 0, TDS 136 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -546,19 +546,19 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#3 (1). Минерализация выше 1000 мг/л: ТС#1 (6160 мг/л) и ТС#2 (1235 мг/л). Распределение: требует санитарного контроля — 1, ограниченно пригодная — 1, высокий риск — 1, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#3 (1). Минерализация выше 1000 мг/л: ТС#1 (6160 мг/л) и ТС#2 (1235 мг/л). Распределение: требует санитарного контроля – 1, ограниченно пригодная – 1, высокий риск – 1, критическая – 1.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>• Перейти к дифференцированному выпасу: снизить нагрузку на слабые участки (ТС#3), продуктивные участки использовать в первую очередь с соблюдением сроков отдыха.
 • Низкая обеспеченность азотом ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • На точках с pH ≥ 8,1 проверить почвы на солонцеватость и карбонатность до планирования мелиоративных мероприятий.
 • Уплотнение на ТС#3: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Источники с E. coli (ТС#3) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
 • Для минерализованных источников (ТС#1, ТС#2) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 550 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 550 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -590,18 +590,18 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (14) и ТС#2 (7). Минерализация во всех пробах в пределах 1000 мг/л. Распределение: требует санитарного контроля — 1, ограниченно пригодная — 1, высокий риск — 1, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (14) и ТС#2 (7). Минерализация во всех пробах в пределах 1000 мг/л. Распределение: требует санитарного контроля – 1, ограниченно пригодная – 1, высокий риск – 1, критическая – 1.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>• Перейти к дифференцированному выпасу: снизить нагрузку на слабые участки (ТС#2), продуктивные участки использовать в первую очередь с соблюдением сроков отдыха.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • На точках с pH ≥ 8,1 проверить почвы на солонцеватость и карбонатность до планирования мелиоративных мероприятий.
 • Уплотнение на ТС#1: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Источники с E. coli (ТС#1, ТС#2) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
-• Как основной источник поения в округе предпочтительна ТС#3 (требует санитарного контроля, E. coli 0, TDS 130 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#3 (требует санитарного контроля, E. coli 0, TDS 130 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -633,16 +633,16 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli не обнаружена. Минерализация выше 1000 мг/л: ТС#3 (1076 мг/л). Повышенная мутность (&gt;5 NTU): ТС#2 и ТС#4. Распределение: ограниченно пригодная — 4.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli не обнаружена. Минерализация выше 1000 мг/л: ТС#3 (1076 мг/л). Повышенная мутность (&gt;5 NTU): ТС#2 и ТС#4. Распределение: ограниченно пригодная – 4.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>• Перейти к дифференцированному выпасу: снизить нагрузку на слабые участки (ТС#1, ТС#2 и ТС#3), продуктивные участки использовать в первую очередь с соблюдением сроков отдыха.
 • Низкая обеспеченность азотом ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • Для минерализованных источников (ТС#3) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#1 (ограниченно пригодная, E. coli 0, TDS 156 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#1 (ограниченно пригодная, E. coli 0, TDS 156 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (1) и ТС#2 (1). Минерализация выше 1000 мг/л: ТС#1 (1080 мг/л), ТС#2 (1085 мг/л) и ТС#3 (3930 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1 и ТС#4. Распределение: ограниченно пригодная — 1, высокий риск — 2, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (1) и ТС#2 (1). Минерализация выше 1000 мг/л: ТС#1 (1080 мг/л), ТС#2 (1085 мг/л) и ТС#3 (3930 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1 и ТС#4. Распределение: ограниченно пригодная – 1, высокий риск – 2, критическая – 1.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>• Требуются восстановительные мероприятия: ограничение выпаса на участках ТС#1, ТС#2 и ТС#3, поверхностное улучшение с подсевом житняка, пырея или костреца.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • Источники с E. coli (ТС#1, ТС#2) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
 • Для минерализованных источников (ТС#1, ТС#2, ТС#3) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#4 (ограниченно пригодная, E. coli 0, TDS 251 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#4 (ограниченно пригодная, E. coli 0, TDS 251 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -716,17 +716,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (2) и ТС#3 (1). Минерализация выше 1000 мг/л: ТС#1 (1350 мг/л) и ТС#2 (1550 мг/л). Распределение: требует санитарного контроля — 1, ограниченно пригодная — 1, высокий риск — 2.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (2) и ТС#3 (1). Минерализация выше 1000 мг/л: ТС#1 (1350 мг/л) и ТС#2 (1550 мг/л). Распределение: требует санитарного контроля – 1, ограниченно пригодная – 1, высокий риск – 2.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>• Сохранить текущий режим использования пастбищ; нагрузку не повышать, вести ежегодный мониторинг покрытия и урожайности.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • Источники с E. coli (ТС#2, ТС#3) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
 • Для минерализованных источников (ТС#1, ТС#2) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 50 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 50 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (130) и ТС#4 (1). Минерализация выше 1000 мг/л: ТС#2 (3020 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1 и ТС#4. Распределение: требует санитарного контроля — 1, ограниченно пригодная — 1, высокий риск — 1, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (130) и ТС#4 (1). Минерализация выше 1000 мг/л: ТС#2 (3020 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1 и ТС#4. Распределение: требует санитарного контроля – 1, ограниченно пригодная – 1, высокий риск – 1, критическая – 1.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>• Сохранить текущий режим использования пастбищ; нагрузку не повышать, вести ежегодный мониторинг покрытия и урожайности.
 • Низкая обеспеченность азотом ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • На точках с pH ≥ 8,1 проверить почвы на солонцеватость и карбонатность до планирования мелиоративных мероприятий.
 • Уплотнение на ТС#3 и ТС#4: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Источники с E. coli (ТС#2, ТС#4) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
 • Для минерализованных источников (ТС#2) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#3 (требует санитарного контроля, E. coli 0, TDS 132 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#3 (требует санитарного контроля, E. coli 0, TDS 132 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -797,23 +797,23 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Проективное покрытие составляет 70–80 %, а средняя высота травостоя всего 6,0–18,5 см. На точке 3 покрытие соответствует II ступени, остальные значения 75–80 % занимают промежуточное положение между нормативными диапазонами I и II. Урожайность зеленой массы составляет менее 5–12,0 ц/га, сухой 2,3–6,2 ц/га. На точках 3 и 4 зеленая масса составляет менее 5 ц/га. На первых точках присутствуют подорожник, клевер и горец птичий, на менее продуктивных — полынь, типчак и ковыль.</t>
+          <t>Проективное покрытие составляет 70–80 %, а средняя высота травостоя всего 6,0–18,5 см. На точке 3 покрытие соответствует II ступени, остальные значения 75–80 % занимают промежуточное положение между нормативными диапазонами I и II. Урожайность зеленой массы составляет менее 5–12,0 ц/га, сухой 2,3–6,2 ц/га. На точках 3 и 4 зеленая масса составляет менее 5 ц/га. На первых точках присутствуют подорожник, клевер и горец птичий, на менее продуктивных – полынь, типчак и ковыль.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (2) и ТС#3 (10). Минерализация выше 1000 мг/л: ТС#3 (3006 мг/л) и ТС#4 (1775 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1. Распределение: ограниченно пригодная — 2, высокий риск — 1, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#1 (2) и ТС#3 (10). Минерализация выше 1000 мг/л: ТС#3 (3006 мг/л) и ТС#4 (1775 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1. Распределение: ограниченно пригодная – 2, высокий риск – 1, критическая – 1.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>• Снизить пастбищную нагрузку и ввести загонно-пастбищную систему с отдыхом участков; на участках со сбоем (ТС#1, ТС#2, ТС#3 и ТС#4) — отдых пастбища на сезон.
+          <t>• Снизить пастбищную нагрузку и ввести загонно-пастбищную систему с отдыхом участков; на участках со сбоем (ТС#1, ТС#2, ТС#3 и ТС#4) – отдых пастбища на сезон.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • Уплотнение на ТС#3: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Источники с E. coli (ТС#1, ТС#3) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
 • Для минерализованных источников (ТС#3, ТС#4) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#2 (ограниченно пригодная, E. coli 0, TDS 125 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#2 (ограниченно пригодная, E. coli 0, TDS 125 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -845,17 +845,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (1) и ТС#3 (1). Минерализация во всех пробах в пределах 1000 мг/л. Повышенная мутность (&gt;5 NTU): ТС#1 и ТС#3. Распределение: ограниченно пригодная — 2, высокий риск — 2.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (1) и ТС#3 (1). Минерализация во всех пробах в пределах 1000 мг/л. Повышенная мутность (&gt;5 NTU): ТС#1 и ТС#3. Распределение: ограниченно пригодная – 2, высокий риск – 2.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>• Сохранить текущий режим использования пастбищ; нагрузку не повышать, вести ежегодный мониторинг покрытия и урожайности.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • На точках с pH ≥ 8,1 проверить почвы на солонцеватость и карбонатность до планирования мелиоративных мероприятий.
 • Источники с E. coli (ТС#2, ТС#3) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
-• Как основной источник поения в округе предпочтительна ТС#4 (ограниченно пригодная, E. coli 0, TDS 130 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#4 (ограниченно пригодная, E. coli 0, TDS 130 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -887,18 +887,18 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli не обнаружена. Минерализация выше 1000 мг/л: ТС#2 (1550 мг/л) и ТС#3 (3320 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1. Распределение: требует санитарного контроля — 1, ограниченно пригодная — 2, критическая — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli не обнаружена. Минерализация выше 1000 мг/л: ТС#2 (1550 мг/л) и ТС#3 (3320 мг/л). Повышенная мутность (&gt;5 NTU): ТС#1. Распределение: требует санитарного контроля – 1, ограниченно пригодная – 2, критическая – 1.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>• Приоритетный округ для восстановления: вывести наиболее деградированные участки (ТС#1, ТС#2, ТС#3 и ТС#4) из выпаса на 2–3 сезона, провести поверхностное улучшение с подсевом многолетних злаков, пересмотреть нагрузку на пастбища округа.
 • Низкая обеспеченность азотом ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • На точках с pH ≥ 8,1 проверить почвы на солонцеватость и карбонатность до планирования мелиоративных мероприятий.
 • Уплотнение на ТС#1, ТС#2 и ТС#4: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Для минерализованных источников (ТС#2, ТС#3) определить солевой состав (хлориды, сульфаты, натрий, жёсткость) и решить вопрос о допустимости поения по видам и возрасту животных.
-• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 805 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 805 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (1). Минерализация во всех пробах в пределах 1000 мг/л. Повышенная мутность (&gt;5 NTU): ТС#2. Распределение: требует санитарного контроля — 1, ограниченно пригодная — 2, высокий риск — 1.</t>
+          <t>Колиформные бактерии обнаружены во всех 4 пробах. E. coli обнаружена: ТС#2 (1). Минерализация во всех пробах в пределах 1000 мг/л. Повышенная мутность (&gt;5 NTU): ТС#2. Распределение: требует санитарного контроля – 1, ограниченно пригодная – 2, высокий риск – 1.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>• Сохранить текущий режим использования пастбищ; нагрузку не повышать, вести ежегодный мониторинг покрытия и урожайности.
 • Низкая обеспеченность азотом и фосфором ограничивает продуктивность травостоя: при улучшении пастбищ и создании сеяных сенокосов предусмотреть внесение азотно-фосфорных удобрений по результатам агрохимического расчёта.
-• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни — травосеяние и органические удобрения.
+• Низкое содержание гумуса: не допускать перевыпаса и сбоя дернины, сохранять растительные остатки; для пашни – травосеяние и органические удобрения.
 • Уплотнение на ТС#4: снизить нагрузку у мест водопоя и скотопрогонов, чередовать места стоянки скота.
 • Источники с E. coli (ТС#2) не использовать для постоянного поения до повторного микробиологического анализа; обследовать зону вокруг источника (скот, навоз, поверхностный сток, оголовок скважины), провести обеззараживание.
-• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 106 мг/л) — при регулярном санитарном контроле.</t>
+• Как основной источник поения в округе предпочтительна ТС#4 (требует санитарного контроля, E. coli 0, TDS 106 мг/л) – при регулярном санитарном контроле.</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Названия округов в первом столбце не меняйте — по ним текст привязывается к карте.</t>
+          <t>Названия округов в первом столбце не меняйте – по ним текст привязывается к карте.</t>
         </is>
       </c>
     </row>
